--- a/viewer/downloads/Grade_8_MN2022_Alignment.xlsx
+++ b/viewer/downloads/Grade_8_MN2022_Alignment.xlsx
@@ -487,7 +487,7 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,12 +554,12 @@
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>CC3 1.1.4 (Scatterplots
-Independent and D); CC3 7.1.2 (Scatterplots &amp; Data); CC3 7.3.2 (Line of Best Fit Equation &amp; As); CC3 7.3.3 (Two-Way Tables &amp; Association)</t>
+Independent and D); CC3 7.1.2 (Scatterplots &amp; Data); CC3 7.1.3 (Scatterplots &amp; Association); CC3 7.3.2 (Line of Best Fit Equation &amp; As); CC3 7.3.3 (Two-Way Tables &amp; Association)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -586,12 +586,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>CC3 7.1.1 (Circle Graphs); CC3 7.1.2 (Scatterplots &amp; Data)</t>
+          <t>CC3 7.1.1 (Circle Graphs); CC3 7.1.2 (Scatterplots &amp; Data); CC3 7.1.3 (Scatterplots &amp; Association)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -618,12 +618,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>CC3 7.3.1 (Line of Best Fit Equation); CC3 7.3.2 (Line of Best Fit Equation &amp; As)</t>
+          <t>CC3 7.1.3 (Scatterplots &amp; Association); CC3 7.3.1 (Line of Best Fit Equation); CC3 7.3.2 (Line of Best Fit Equation &amp; As)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -650,12 +650,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>CC3 7.1.2 (Scatterplots &amp; Data); CC3 7.3.2 (Line of Best Fit Equation &amp; As)</t>
+          <t>CC3 7.1.2 (Scatterplots &amp; Data); CC3 7.1.3 (Scatterplots &amp; Association); CC3 7.3.2 (Line of Best Fit Equation &amp; As)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>CC3 1.1.4 (Scatterplots
-Independent and D); CC3 7.3.2 (Line of Best Fit Equation &amp; As)</t>
+Independent and D); CC3 7.1.3 (Scatterplots &amp; Association); CC3 7.3.2 (Line of Best Fit Equation &amp; As)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>CC3 1.1.4 (Scatterplots
-Independent and D); CC3 7.1.2 (Scatterplots &amp; Data); CC3 7.3.2 (Line of Best Fit Equation &amp; As)</t>
+Independent and D); CC3 7.1.2 (Scatterplots &amp; Data); CC3 7.1.3 (Scatterplots &amp; Association); CC3 7.3.2 (Line of Best Fit Equation &amp; As)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -748,12 +748,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>CC3 9.1.1 (Parallel Lines Cut by a Transv); CC3 9.1.2 (Triangle Angle Sum); CC3 9.1.3 (Exterior Angles of Triangles)</t>
+          <t>CC3 10.1.4 (Volume of Sphere); CC3 10.1.5 (Volume in Context); CC3 6.1.1 (Rigid Transformations); CC3 6.1.2 (Rigid Transformations); CC3 6.1.3 (Rigid Transformations); CC3 6.1.4 (Rigid Transformations); CC3 6.2.3 (Similarity, Congruence, and Sc); CC3 6.2.4 (Similar Figures &amp; Transformati); CC3 6.2.5 (Similar Figures); CC3 6.2.6 (Similar Figures); CC3 9.1.1 (Parallel Lines Cut by a Transv); CC3 9.1.2 (Triangle Angle Sum); CC3 9.1.3 (Exterior Angles of Triangles); CC3 9.2.1 (Right, Acute and Obtuse Triang); CC3 9.2.2 (Right Triangles &amp; Pythagorean ); CC3 9.2.5 (Pythagorean Theorem in Context); CC3 9.2.6 (Pythagorean Theorem in 3-D)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>CC3 9.1.1 (Parallel Lines Cut by a Transv); CC3 9.1.2 (Triangle Angle Sum)</t>
+          <t>CC3 10.1.4 (Volume of Sphere); CC3 10.1.5 (Volume in Context); CC3 6.1.1 (Rigid Transformations); CC3 6.1.2 (Rigid Transformations); CC3 6.1.3 (Rigid Transformations); CC3 6.1.4 (Rigid Transformations); CC3 6.2.3 (Similarity, Congruence, and Sc); CC3 6.2.4 (Similar Figures &amp; Transformati); CC3 6.2.5 (Similar Figures); CC3 6.2.6 (Similar Figures); CC3 9.1.1 (Parallel Lines Cut by a Transv); CC3 9.1.2 (Triangle Angle Sum); CC3 9.2.1 (Right, Acute and Obtuse Triang); CC3 9.2.2 (Right Triangles &amp; Pythagorean ); CC3 9.2.5 (Pythagorean Theorem in Context); CC3 9.2.6 (Pythagorean Theorem in 3-D)</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>CC3 9.1.1 (Parallel Lines Cut by a Transv)</t>
+          <t>CC3 10.1.4 (Volume of Sphere); CC3 10.1.5 (Volume in Context); CC3 6.1.1 (Rigid Transformations); CC3 6.1.2 (Rigid Transformations); CC3 6.1.3 (Rigid Transformations); CC3 6.1.4 (Rigid Transformations); CC3 6.2.3 (Similarity, Congruence, and Sc); CC3 6.2.4 (Similar Figures &amp; Transformati); CC3 6.2.5 (Similar Figures); CC3 6.2.6 (Similar Figures); CC3 9.1.1 (Parallel Lines Cut by a Transv); CC3 9.2.1 (Right, Acute and Obtuse Triang); CC3 9.2.2 (Right Triangles &amp; Pythagorean ); CC3 9.2.5 (Pythagorean Theorem in Context); CC3 9.2.6 (Pythagorean Theorem in 3-D)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>CC3 3.1.2 (Writing Algebraic Equations); CC3 3.1.6 (Graphing Equations); CC3 7.2.1 (Linear graphs and equations); CC3 8.1.1 (Linear &amp; Nonlinear Tables &amp; Gr); CC3 8.1.3 (Simple Interest (Linear) &amp; Com)</t>
+          <t>CC3 10.1.4 (Volume of Sphere); CC3 10.1.5 (Volume in Context); CC3 3.1.2 (Writing Algebraic Equations); CC3 3.1.6 (Graphing Equations); CC3 6.1.1 (Rigid Transformations); CC3 6.1.2 (Rigid Transformations); CC3 6.1.3 (Rigid Transformations); CC3 6.1.4 (Rigid Transformations); CC3 6.2.3 (Similarity, Congruence, and Sc); CC3 6.2.4 (Similar Figures &amp; Transformati); CC3 6.2.5 (Similar Figures); CC3 6.2.6 (Similar Figures); CC3 7.2.1 (Linear graphs and equations); CC3 8.1.1 (Linear &amp; Nonlinear Tables &amp; Gr); CC3 8.1.3 (Simple Interest (Linear) &amp; Com); CC3 9.2.1 (Right, Acute and Obtuse Triang); CC3 9.2.2 (Right Triangles &amp; Pythagorean ); CC3 9.2.5 (Pythagorean Theorem in Context); CC3 9.2.6 (Pythagorean Theorem in 3-D)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>CC3 7.2.1 (Linear graphs and equations)</t>
+          <t>CC3 10.1.4 (Volume of Sphere); CC3 10.1.5 (Volume in Context); CC3 6.1.1 (Rigid Transformations); CC3 6.1.2 (Rigid Transformations); CC3 6.1.3 (Rigid Transformations); CC3 6.1.4 (Rigid Transformations); CC3 6.2.3 (Similarity, Congruence, and Sc); CC3 6.2.4 (Similar Figures &amp; Transformati); CC3 6.2.5 (Similar Figures); CC3 6.2.6 (Similar Figures); CC3 7.2.1 (Linear graphs and equations); CC3 9.2.1 (Right, Acute and Obtuse Triang); CC3 9.2.2 (Right Triangles &amp; Pythagorean ); CC3 9.2.5 (Pythagorean Theorem in Context); CC3 9.2.6 (Pythagorean Theorem in 3-D)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>CC3 5.2.4 (Sovling Systems)</t>
+          <t>CC3 10.1.4 (Volume of Sphere); CC3 10.1.5 (Volume in Context); CC3 5.2.4 (Sovling Systems); CC3 6.1.1 (Rigid Transformations); CC3 6.1.2 (Rigid Transformations); CC3 6.1.3 (Rigid Transformations); CC3 6.1.4 (Rigid Transformations); CC3 6.2.3 (Similarity, Congruence, and Sc); CC3 6.2.4 (Similar Figures &amp; Transformati); CC3 6.2.5 (Similar Figures); CC3 6.2.6 (Similar Figures); CC3 9.2.1 (Right, Acute and Obtuse Triang); CC3 9.2.2 (Right Triangles &amp; Pythagorean ); CC3 9.2.5 (Pythagorean Theorem in Context); CC3 9.2.6 (Pythagorean Theorem in 3-D)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,13 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>CC3 9.1.4 (AA Triangle Similarity)</t>
+          <t>CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 4.1.4 (Writing Linear Equations); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 8.2.2 (Simplifying Exponents (Propert); CC3 9.1.4 (AA Triangle Similarity); CC3 9.2.3 (Square Root and Irrational Num); CC3 9.2.4 (Rational vs. Irrational Number)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -972,12 +973,13 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>CC3 9.1.3 (Exterior Angles of Triangles); CC3 9.1.4 (AA Triangle Similarity)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.2.3 (Solving Equations); CC3 4.1.4 (Writing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 8.2.2 (Simplifying Exponents (Propert); CC3 9.1.3 (Exterior Angles of Triangles); CC3 9.1.4 (AA Triangle Similarity); CC3 9.2.3 (Square Root and Irrational Num); CC3 9.2.4 (Rational vs. Irrational Number)</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1006,13 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>CC3 8.2.1 (Positive Exponents &amp; Scientifi); CC3 8.2.3 (Negative Exponents &amp; Scientifi)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.2.3 (Solving Equations); CC3 4.1.4 (Writing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 8.2.1 (Positive Exponents &amp; Scientifi); CC3 8.2.2 (Simplifying Exponents (Propert); CC3 8.2.3 (Negative Exponents &amp; Scientifi); CC3 9.2.3 (Square Root and Irrational Num); CC3 9.2.4 (Rational vs. Irrational Number)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1039,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>CC3 8.2.1 (Positive Exponents &amp; Scientifi); CC3 8.2.4 (Operations with Scientific Not)</t>
+          <t>CC3 8.2.1 (Positive Exponents &amp; Scientifi); CC3 8.2.2 (Simplifying Exponents (Propert); CC3 8.2.4 (Operations with Scientific Not)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1071,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>CC3 8.2.1 (Positive Exponents &amp; Scientifi); CC3 8.2.4 (Operations with Scientific Not)</t>
+          <t>CC3 8.2.1 (Positive Exponents &amp; Scientifi); CC3 8.2.2 (Simplifying Exponents (Propert); CC3 8.2.4 (Operations with Scientific Not)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1103,13 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>CC3 8.1.1 (Linear &amp; Nonlinear Tables &amp; Gr); CC3 8.1.2 (Compound Interest); CC3 8.1.3 (Simple Interest (Linear) &amp; Com)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.2.3 (Solving Equations); CC3 4.1.4 (Writing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 8.1.1 (Linear &amp; Nonlinear Tables &amp; Gr); CC3 8.1.2 (Compound Interest); CC3 8.1.3 (Simple Interest (Linear) &amp; Com)</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1136,13 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>CC3 8.1.1 (Linear &amp; Nonlinear Tables &amp; Gr); CC3 8.1.2 (Compound Interest); CC3 8.1.3 (Simple Interest (Linear) &amp; Com)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.2.3 (Solving Equations); CC3 4.1.4 (Writing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 8.1.1 (Linear &amp; Nonlinear Tables &amp; Gr); CC3 8.1.2 (Compound Interest); CC3 8.1.3 (Simple Interest (Linear) &amp; Com)</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1169,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>CC3 7.2.1 (Linear graphs and equations)</t>
+          <t>CC3 1.1.2 (Pattern Recognition); CC3 3.1.4 (Graphing Data); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 7.2.1 (Linear graphs and equations)</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1196,15 +1201,16 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>CC3 2.1.2 (Area and Perimeter
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 2.1.2 (Area and Perimeter
 Simplyfiin); CC3 2.1.5 (Inequalities
 Simplifying Expr); CC3 2.1.7 (Inequalities
-Simplifying Agle); CC3 3.2.5 (Solving Equations)</t>
+Simplifying Agle); CC3 3.2.3 (Solving Equations); CC3 3.2.5 (Solving Equations); CC3 4.1.4 (Writing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1237,14 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>CC3 2.1.4 (Zero Pairs
-Simplifying Aglebr)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 2.1.4 (Zero Pairs
+Simplifying Aglebr); CC3 3.2.3 (Solving Equations); CC3 4.1.4 (Writing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 9.2.3 (Square Root and Irrational Num); CC3 9.2.4 (Rational vs. Irrational Number)</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1271,13 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>CC3 2.1.8 (Simplifying and Solving Aglebr); CC3 2.1.9 (Simplifying and Solving Aglebr); CC3 3.2.1 (Solving Equations); CC3 3.2.2 (Solving Equations); CC3 3.2.5 (Solving Equations); CC3 5.1.1 (Isolating Variables in Equatio); CC3 5.1.2 (Solving equations with Fractio)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 2.1.8 (Simplifying and Solving Aglebr); CC3 2.1.9 (Simplifying and Solving Aglebr); CC3 3.1.4 (Graphing Data); CC3 3.2.1 (Solving Equations); CC3 3.2.2 (Solving Equations); CC3 3.2.3 (Solving Equations); CC3 3.2.5 (Solving Equations); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.4 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 5.1.1 (Isolating Variables in Equatio); CC3 5.1.2 (Solving equations with Fractio); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1304,13 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>CC3 9.1.3 (Exterior Angles of Triangles); CC3 9.1.4 (AA Triangle Similarity)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.2.3 (Solving Equations); CC3 4.1.4 (Writing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 8.2.2 (Simplifying Exponents (Propert); CC3 9.1.3 (Exterior Angles of Triangles); CC3 9.1.4 (AA Triangle Similarity)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1337,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>CC3 4.1.3 (Graphing Linear Equations); CC3 4.1.5 (Making Connections between Rep); CC3 7.2.1 (Linear graphs and equations)</t>
+          <t>CC3 1.1.2 (Pattern Recognition); CC3 3.1.4 (Graphing Data); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.3 (Graphing Linear Equations); CC3 4.1.5 (Making Connections between Rep); CC3 4.1.6 (Graphing Linear Equations); CC3 7.2.1 (Linear graphs and equations)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1369,13 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>CC3 4.1.3 (Graphing Linear Equations); CC3 4.1.5 (Making Connections between Rep); CC3 7.2.1 (Linear graphs and equations)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.1.4 (Graphing Data); CC3 3.2.3 (Solving Equations); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.3 (Graphing Linear Equations); CC3 4.1.4 (Writing Linear Equations); CC3 4.1.5 (Making Connections between Rep); CC3 4.1.6 (Graphing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.1 (Linear graphs and equations); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope)</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1402,13 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>CC3 10.1.1 (Volume and Cube Roots); CC3 10.1.2 (Surface Area &amp; Volume of Cylin)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 10.1.1 (Volume and Cube Roots); CC3 10.1.2 (Surface Area &amp; Volume of Cylin); CC3 3.1.4 (Graphing Data); CC3 3.2.3 (Solving Equations); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.4 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 9.2.3 (Square Root and Irrational Num); CC3 9.2.4 (Rational vs. Irrational Number)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1424,13 +1435,14 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>CC3 10.1.3 (Volume of a Cylinder vs Cone 
-)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 10.1.3 (Volume of a Cylinder vs Cone 
+); CC3 3.1.4 (Graphing Data); CC3 3.2.3 (Solving Equations); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.4 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 9.2.3 (Square Root and Irrational Num); CC3 9.2.4 (Rational vs. Irrational Number)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1469,13 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>CC3 10.2.1 (Indirect Measurement); CC3 10.4.2 (); CC3 5.2.1 (Introduce Systems of Equations); CC3 5.2.4 (Sovling Systems)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 10.2.1 (Indirect Measurement); CC3 10.4.2 (); CC3 3.1.4 (Graphing Data); CC3 3.2.3 (Solving Equations); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.4 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 5.2.1 (Introduce Systems of Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 5.2.4 (Sovling Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1502,13 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>CC3 3.1.2 (Writing Algebraic Equations); CC3 3.1.5 (Graphing Data); CC3 3.2.4 (Solving Equations); CC3 4.1.1 (Pattern Recognition); CC3 4.1.7 (Making Connections between Rep); CC3 7.2.1 (Linear graphs and equations); CC3 7.2.5 (Proportional Equations)</t>
+          <t>CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.1.2 (Writing Algebraic Equations); CC3 3.1.4 (Graphing Data); CC3 3.1.5 (Graphing Data); CC3 3.2.4 (Solving Equations); CC3 4.1.1 (Pattern Recognition); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.4 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 4.1.7 (Making Connections between Rep); CC3 7.2.1 (Linear graphs and equations); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 7.2.5 (Proportional Equations)</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1535,13 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>CC3 3.1.1 (Connecting Rules and Patterns); CC3 3.1.3 (Graphing Equations); CC3 4.1.1 (Pattern Recognition); CC3 4.1.3 (Graphing Linear Equations); CC3 4.1.7 (Making Connections between Rep)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.1.1 (Connecting Rules and Patterns); CC3 3.1.3 (Graphing Equations); CC3 3.1.4 (Graphing Data); CC3 3.2.3 (Solving Equations); CC3 4.1.1 (Pattern Recognition); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.3 (Graphing Linear Equations); CC3 4.1.4 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 4.1.7 (Making Connections between Rep); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1568,13 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>CC3 3.1.2 (Writing Algebraic Equations); CC3 3.1.6 (Graphing Equations); CC3 7.2.1 (Linear graphs and equations); CC3 8.1.1 (Linear &amp; Nonlinear Tables &amp; Gr); CC3 8.1.3 (Simple Interest (Linear) &amp; Com); CC3 8.3.1 (Intro to Functions)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.1.2 (Writing Algebraic Equations); CC3 3.1.4 (Graphing Data); CC3 3.1.6 (Graphing Equations); CC3 3.2.3 (Solving Equations); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.4 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.1 (Linear graphs and equations); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 8.1.1 (Linear &amp; Nonlinear Tables &amp; Gr); CC3 8.1.3 (Simple Interest (Linear) &amp; Com); CC3 8.2.2 (Simplifying Exponents (Propert); CC3 8.3.1 (Intro to Functions); CC3 9.2.3 (Square Root and Irrational Num); CC3 9.2.4 (Rational vs. Irrational Number)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1601,13 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>CC3 3.1.2 (Writing Algebraic Equations); CC3 3.1.7 (Interpreting Graphs); CC3 4.1.1 (Pattern Recognition); CC3 4.1.7 (Making Connections between Rep)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.1.2 (Writing Algebraic Equations); CC3 3.1.4 (Graphing Data); CC3 3.1.7 (Interpreting Graphs); CC3 3.2.3 (Solving Equations); CC3 4.1.1 (Pattern Recognition); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.4 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 4.1.7 (Making Connections between Rep); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1634,13 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>CC3 4.1.3 (Graphing Linear Equations)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.1.4 (Graphing Data); CC3 3.2.3 (Solving Equations); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.3 (Graphing Linear Equations); CC3 4.1.4 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1668,13 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>CC3 3.1.1 (Connecting Rules and Patterns); CC3 3.1.7 (Interpreting Graphs); CC3 4.1.1 (Pattern Recognition); CC3 4.1.7 (Making Connections between Rep); CC3 7.2.1 (Linear graphs and equations); CC3 8.3.1 (Intro to Functions)</t>
+          <t>CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.1.1 (Connecting Rules and Patterns); CC3 3.1.4 (Graphing Data); CC3 3.1.7 (Interpreting Graphs); CC3 4.1.1 (Pattern Recognition); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.4 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 4.1.7 (Making Connections between Rep); CC3 7.2.1 (Linear graphs and equations); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope); CC3 8.3.1 (Intro to Functions)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1701,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>CC3 6.2.1 (Dilations); CC3 6.2.2 (Dilations and Similarity)</t>
+          <t>CC3 1.1.2 (Pattern Recognition); CC3 3.1.4 (Graphing Data); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 6.2.1 (Dilations); CC3 6.2.2 (Dilations and Similarity)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1733,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>CC3 6.2.1 (Dilations); CC3 6.2.2 (Dilations and Similarity)</t>
+          <t>CC3 1.1.2 (Pattern Recognition); CC3 3.1.4 (Graphing Data); CC3 4.1.2 (Writing Linear Equations); CC3 4.1.6 (Graphing Linear Equations); CC3 6.2.1 (Dilations); CC3 6.2.2 (Dilations and Similarity)</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1765,13 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>CC3 6.2.1 (Dilations); CC3 6.2.2 (Dilations and Similarity)</t>
+          <t>CC2 1.1.3 (Variables and Solutions); CC3 1.1.2 (Pattern Recognition); CC3 1.1.3 (Coordinate Plane
+Linear Graphs); CC3 1.2.1 (Proportinal Relationships); CC3 3.2.3 (Solving Equations); CC3 4.1.4 (Writing Linear Equations); CC3 5.2.2 (Writing Rules from Word Proble); CC3 5.2.3 (Solving Systems); CC3 6.2.1 (Dilations); CC3 6.2.2 (Dilations and Similarity); CC3 7.2.2 (Slope); CC3 7.2.3 (Slope); CC3 7.2.4 (Slope)</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
